--- a/diseases/d032/1985-1989.xlsx
+++ b/diseases/d032/1985-1989.xlsx
@@ -2183,7 +2183,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">

--- a/diseases/d032/1985-1989.xlsx
+++ b/diseases/d032/1985-1989.xlsx
@@ -2183,7 +2183,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">

--- a/diseases/d032/1985-1989.xlsx
+++ b/diseases/d032/1985-1989.xlsx
@@ -1935,11 +1935,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
@@ -1957,17 +1952,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -1976,12 +1961,7 @@
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -2047,7 +2027,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2082,12 +2062,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1987-01-01</t>
+          <t>1987-02-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1987-01</t>
+          <t>1987-02</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -2101,126 +2081,28 @@
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN9" t="b">
+      <c r="AT9" t="n">
         <v>1</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -2321,24 +2203,19 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1987-02-01</t>
+          <t>1987-03-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1987-02</t>
+          <t>1987-03</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -2357,17 +2234,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -2376,12 +2243,7 @@
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2447,7 +2309,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2482,12 +2344,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1987-02-01</t>
+          <t>1987-04-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1987-02</t>
+          <t>1987-04</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2501,126 +2363,28 @@
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN11" t="b">
+      <c r="AT11" t="n">
         <v>1</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2721,67 +2485,47 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1987-03-01</t>
+          <t>1987-05-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1987-03</t>
+          <t>1987-05</t>
         </is>
       </c>
       <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
         <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2847,7 +2591,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2882,145 +2626,47 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1987-03-01</t>
+          <t>1987-06-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1987-03</t>
+          <t>1987-06</t>
         </is>
       </c>
       <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
         <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -3121,12 +2767,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1987-04-01</t>
+          <t>1987-07-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1987-04</t>
+          <t>1987-07</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -3135,11 +2781,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
@@ -3157,17 +2798,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -3176,12 +2807,7 @@
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -3247,7 +2873,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3282,12 +2908,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1987-04-01</t>
+          <t>1987-08-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1987-04</t>
+          <t>1987-08</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -3301,126 +2927,28 @@
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN15" t="b">
+      <c r="AT15" t="n">
         <v>1</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -3521,12 +3049,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1987-05-01</t>
+          <t>1987-09-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1987-05</t>
+          <t>1987-09</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3535,11 +3063,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
@@ -3557,17 +3080,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -3576,12 +3089,7 @@
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3647,7 +3155,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3682,12 +3190,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1987-05-01</t>
+          <t>1987-10-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1987-05</t>
+          <t>1987-10</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3701,126 +3209,28 @@
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN17" t="b">
+      <c r="AT17" t="n">
         <v>1</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3921,12 +3331,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1987-06-01</t>
+          <t>1987-11-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1987-06</t>
+          <t>1987-11</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -3935,11 +3345,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
@@ -3957,17 +3362,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -3976,12 +3371,7 @@
         </is>
       </c>
       <c r="AT18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -4047,7 +3437,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4082,12 +3472,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1987-06-01</t>
+          <t>1987-12-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1987-06</t>
+          <t>1987-12</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -4101,126 +3491,28 @@
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN19" t="b">
+      <c r="AT19" t="n">
         <v>1</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -4291,12 +3583,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -4321,19 +3613,19 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1987-07-01</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1987-07</t>
+          <t>1988-01</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -4342,12 +3634,12 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -4357,7 +3649,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -4365,62 +3657,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
         </is>
       </c>
       <c r="AT20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -4452,12 +3739,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -4482,38 +3769,38 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1987-07-01</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1987-07</t>
+          <t>1988-01</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Brucellose</t>
+          <t>Brucellosis</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -4523,12 +3810,12 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -4538,7 +3825,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -4573,17 +3860,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4596,7 +3883,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -4604,62 +3891,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
         </is>
       </c>
       <c r="AT21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -4691,12 +3973,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -4721,19 +4003,19 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1987-08-01</t>
+          <t>1989-01-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1987-08</t>
+          <t>1989-01</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -4742,12 +4024,12 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -4757,7 +4039,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -4765,62 +4047,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
         </is>
       </c>
       <c r="AT22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4129,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -4882,38 +4159,38 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1987-08-01</t>
+          <t>1989-01-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1987-08</t>
+          <t>1989-01</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Brucellose</t>
+          <t>Brucellosis</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -4923,12 +4200,12 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -4938,7 +4215,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -4973,17 +4250,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -4996,7 +4273,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
@@ -5004,2440 +4281,55 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
         </is>
       </c>
       <c r="AT23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>brucellosis</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>布鲁氏菌病</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>1987-09-01</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>1987-09</t>
-        </is>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP24" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
-      </c>
-      <c r="AV24" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="BA24" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="BB24" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="BC24" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>brucellosis</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>布鲁氏菌病</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>1987-09-01</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>1987-09</t>
-        </is>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG25" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP25" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
-      </c>
-      <c r="AV25" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="BA25" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="BB25" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="BC25" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>brucellosis</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>布鲁氏菌病</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>1987-10-01</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>1987-10</t>
-        </is>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP26" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ26" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS26" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
-      </c>
-      <c r="AV26" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="BA26" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="BB26" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="BC26" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>brucellosis</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>布鲁氏菌病</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>1987-10-01</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>1987-10</t>
-        </is>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG27" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP27" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ27" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS27" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
-      </c>
-      <c r="AV27" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="BA27" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="BB27" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="BC27" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>brucellosis</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>布鲁氏菌病</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>1987-11-01</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>1987-11</t>
-        </is>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP28" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ28" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS28" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
-      </c>
-      <c r="AV28" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="BA28" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="BB28" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="BC28" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>brucellosis</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>布鲁氏菌病</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>1987-11-01</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>1987-11</t>
-        </is>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP29" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ29" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
-      </c>
-      <c r="AV29" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="BA29" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="BB29" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="BC29" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>brucellosis</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>布鲁氏菌病</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>1987-12-01</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>1987-12</t>
-        </is>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP30" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ30" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS30" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
-      </c>
-      <c r="AV30" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="BA30" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="BB30" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="BC30" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>brucellosis</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>布鲁氏菌病</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>1987-12-01</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>1987-12</t>
-        </is>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG31" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP31" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ31" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
-      </c>
-      <c r="AV31" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="BA31" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="BB31" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="BC31" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>brucellosis</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>布鲁氏菌病</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>1988-01-01</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>1988-01</t>
-        </is>
-      </c>
-      <c r="N32" t="n">
-        <v>13</v>
-      </c>
-      <c r="O32" t="n">
-        <v>13</v>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP32" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV32" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Canada PHAC CNDSS Annual</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="BA32" t="inlineStr">
-        <is>
-          <t>Canada PHAC CNDSS Annual</t>
-        </is>
-      </c>
-      <c r="BB32" t="inlineStr">
-        <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
-        </is>
-      </c>
-      <c r="BC32" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>brucellosis</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>布鲁氏菌病</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>1988-01-01</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>1988-01</t>
-        </is>
-      </c>
-      <c r="N33" t="n">
-        <v>13</v>
-      </c>
-      <c r="O33" t="n">
-        <v>13</v>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP33" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS33" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV33" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Canada PHAC CNDSS Annual</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="BA33" t="inlineStr">
-        <is>
-          <t>Canada PHAC CNDSS Annual</t>
-        </is>
-      </c>
-      <c r="BB33" t="inlineStr">
-        <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
-        </is>
-      </c>
-      <c r="BC33" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>brucellosis</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>布鲁氏菌病</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>1989-01-01</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>1989-01</t>
-        </is>
-      </c>
-      <c r="N34" t="n">
-        <v>13</v>
-      </c>
-      <c r="O34" t="n">
-        <v>13</v>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP34" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV34" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Canada PHAC CNDSS Annual</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="BA34" t="inlineStr">
-        <is>
-          <t>Canada PHAC CNDSS Annual</t>
-        </is>
-      </c>
-      <c r="BB34" t="inlineStr">
-        <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
-        </is>
-      </c>
-      <c r="BC34" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>brucellosis</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>布鲁氏菌病</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>1989-01-01</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>1989-01</t>
-        </is>
-      </c>
-      <c r="N35" t="n">
-        <v>13</v>
-      </c>
-      <c r="O35" t="n">
-        <v>13</v>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG35" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP35" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV35" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Canada PHAC CNDSS Annual</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="BA35" t="inlineStr">
-        <is>
-          <t>Canada PHAC CNDSS Annual</t>
-        </is>
-      </c>
-      <c r="BB35" t="inlineStr">
-        <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
-        </is>
-      </c>
-      <c r="BC35" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -7569,7 +4461,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -7589,7 +4481,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -7599,7 +4491,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d032/1985-1989.xlsx
+++ b/diseases/d032/1985-1989.xlsx
@@ -1935,6 +1935,11 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
@@ -1952,7 +1957,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -1961,7 +1976,12 @@
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -2027,7 +2047,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2062,12 +2082,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1987-02-01</t>
+          <t>1987-01-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1987-02</t>
+          <t>1987-01</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -2081,11 +2101,94 @@
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Brucellose</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN9" t="b">
+        <v>1</v>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -2093,7 +2196,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -2102,7 +2215,12 @@
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -2203,19 +2321,24 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1987-03-01</t>
+          <t>1987-02-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1987-03</t>
+          <t>1987-02</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -2234,7 +2357,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -2243,7 +2376,12 @@
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2309,7 +2447,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2344,12 +2482,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1987-04-01</t>
+          <t>1987-02-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1987-04</t>
+          <t>1987-02</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2363,11 +2501,94 @@
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Brucellose</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN11" t="b">
+        <v>1</v>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -2375,7 +2596,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -2384,7 +2615,12 @@
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2485,19 +2721,24 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1987-05-01</t>
+          <t>1987-03-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1987-05</t>
+          <t>1987-03</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -2516,7 +2757,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -2525,7 +2776,12 @@
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2591,7 +2847,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2626,30 +2882,113 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1987-06-01</t>
+          <t>1987-03-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1987-06</t>
+          <t>1987-03</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Brucellose</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN13" t="b">
+        <v>1</v>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -2657,7 +2996,17 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -2666,7 +3015,12 @@
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2767,12 +3121,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1987-07-01</t>
+          <t>1987-04-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1987-07</t>
+          <t>1987-04</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2781,6 +3135,11 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
@@ -2798,7 +3157,17 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -2807,7 +3176,12 @@
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2873,7 +3247,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2908,12 +3282,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1987-08-01</t>
+          <t>1987-04-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1987-08</t>
+          <t>1987-04</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2927,11 +3301,94 @@
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Brucellose</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN15" t="b">
+        <v>1</v>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -2939,7 +3396,17 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -2948,7 +3415,12 @@
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -3049,12 +3521,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1987-09-01</t>
+          <t>1987-05-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1987-09</t>
+          <t>1987-05</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3063,6 +3535,11 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
@@ -3080,7 +3557,17 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -3089,7 +3576,12 @@
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3155,7 +3647,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3190,12 +3682,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1987-10-01</t>
+          <t>1987-05-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1987-10</t>
+          <t>1987-05</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3209,11 +3701,94 @@
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Brucellose</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN17" t="b">
+        <v>1</v>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -3221,7 +3796,17 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -3230,7 +3815,12 @@
         </is>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3331,12 +3921,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1987-11-01</t>
+          <t>1987-06-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1987-11</t>
+          <t>1987-06</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -3345,6 +3935,11 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
@@ -3362,7 +3957,17 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -3371,7 +3976,12 @@
         </is>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3437,7 +4047,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3472,12 +4082,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1987-12-01</t>
+          <t>1987-06-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1987-12</t>
+          <t>1987-06</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -3491,11 +4101,94 @@
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Brucellose</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN19" t="b">
+        <v>1</v>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -3503,7 +4196,17 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -3512,7 +4215,12 @@
         </is>
       </c>
       <c r="AT19" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3583,12 +4291,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3613,19 +4321,19 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
+          <t>1987-07-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1988-01</t>
+          <t>1987-07</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -3634,12 +4342,12 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3649,7 +4357,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -3657,57 +4365,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AT20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -3739,12 +4452,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3769,38 +4482,38 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
+          <t>1987-07-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1988-01</t>
+          <t>1987-07</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Brucellosis</t>
+          <t>Brucellose</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3810,12 +4523,12 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3825,7 +4538,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>country:CA:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -3860,17 +4573,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -3883,7 +4596,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -3891,57 +4604,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AT21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -3973,12 +4691,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -4003,19 +4721,19 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1989-01-01</t>
+          <t>1987-08-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1989-01</t>
+          <t>1987-08</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -4024,12 +4742,12 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -4039,7 +4757,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -4047,57 +4765,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AT22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -4129,12 +4852,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -4159,38 +4882,38 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1989-01-01</t>
+          <t>1987-08-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1989-01</t>
+          <t>1987-08</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Brucellosis</t>
+          <t>Brucellose</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -4200,12 +4923,12 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -4215,7 +4938,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>country:CA:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -4250,17 +4973,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -4273,63 +4996,2448 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1987-09-01</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>1987-09</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1987-09-01</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>1987-09</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Brucellose</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1987-10-01</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>1987-10</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1987-10-01</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1987-10</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Brucellose</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1987-11-01</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>1987-11</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1987-11-01</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>1987-11</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Brucellose</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1987-12-01</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>1987-12</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1987-12-01</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>1987-12</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Brucellose</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1988-01-01</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>1988-01</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>13</v>
+      </c>
+      <c r="O32" t="n">
+        <v>13</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ23" t="inlineStr">
+      <c r="AQ32" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS23" t="inlineStr">
+      <c r="AS32" t="inlineStr">
         <is>
           <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
         </is>
       </c>
-      <c r="AT23" t="n">
+      <c r="AT32" t="n">
         <v>1</v>
       </c>
-      <c r="AU23" t="inlineStr">
+      <c r="AU32" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV23" t="inlineStr">
+      <c r="AV32" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AW23" t="inlineStr">
+      <c r="AW32" t="inlineStr">
         <is>
           <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
+      <c r="AX32" t="inlineStr">
         <is>
           <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr">
+      <c r="AY32" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
+      <c r="AZ32" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="BA23" t="inlineStr">
+      <c r="BA32" t="inlineStr">
         <is>
           <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
-      <c r="BB23" t="inlineStr">
+      <c r="BB32" t="inlineStr">
         <is>
           <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
-      <c r="BC23" t="inlineStr">
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>1988-01-01</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>1988-01</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>13</v>
+      </c>
+      <c r="O33" t="n">
+        <v>13</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>1989-01-01</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>1989-01</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>13</v>
+      </c>
+      <c r="O34" t="n">
+        <v>13</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>1989-01-01</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>1989-01</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>13</v>
+      </c>
+      <c r="O35" t="n">
+        <v>13</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D15_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -4461,7 +7569,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
@@ -4481,7 +7589,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -4491,7 +7599,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
